--- a/tests/SafeOpenXml.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R74ea294780be49b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R37a9c65a96094007"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R37a9c65a96094007"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1b73924e50254337"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1b73924e50254337"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5119bdee0bc54669"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5119bdee0bc54669"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8c45678ebbc34f16"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8c45678ebbc34f16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbc4431d3b8134640"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbc4431d3b8134640"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R56f1066b48a94368"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R56f1066b48a94368"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra33a33a0db9c4fdd"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra33a33a0db9c4fdd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0977a885766b44cd"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0977a885766b44cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ree9edfb026684f0b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ree9edfb026684f0b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8839c6ffa28b49a3"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8839c6ffa28b49a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R33d55a359fc3442c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R33d55a359fc3442c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2e30118bb9fa4210"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2e30118bb9fa4210"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbc04027e06bb404e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbc04027e06bb404e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R67d075213e28496b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R67d075213e28496b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb0f24c34a2de403f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb0f24c34a2de403f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc285e059587c43bd"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc285e059587c43bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R667321bb47414968"/>
   </x:sheets>
 </x:workbook>
 </file>
